--- a/Sensitivity_PSNR_Boats.xlsx
+++ b/Sensitivity_PSNR_Boats.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\esray\Desktop\comparison_figures\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2EE34D3-D0D7-45BF-B7B3-0F7EAC2FDE48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3776D284-3600-404E-BC56-07220927C6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2BE9D71-0D34-4F69-BE98-4CA8B55A0AC4}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6AA122F0-38E5-4CEE-A586-8AB4B5A97B66}"/>
   </bookViews>
   <sheets>
     <sheet name="Sayfa1" sheetId="1" r:id="rId1"/>
@@ -32,6 +32,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
@@ -442,7 +445,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439B4879-DB02-4BE7-8243-F7246C2D33F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E368EE1A-662E-44E5-8BCC-D41E86F1208C}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -576,7 +579,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3430E7FC-5337-4BBC-A76E-2DED051144BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EE6779D-C921-4B94-A7AF-12BFEF1B7EBD}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
@@ -585,7 +588,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B0234FE-B8C3-4CA7-8BD0-6B5D2E27D905}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3520FF9-E85D-47AB-8242-3D1D338D7340}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
